--- a/Master Plan.xlsx
+++ b/Master Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bai tap lon\đồ án 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5512F98B-E710-495A-9E9E-275C4A79E142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590143E7-E32F-4C1C-BD3C-69A68B10C7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5690" yWindow="2010" windowWidth="19200" windowHeight="11170" xr2:uid="{7FC3E05B-C07F-48D6-AC4B-6D80727349EB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>Công việc</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Thiết kế các giao diện cho các vai trò của Admin</t>
   </si>
   <si>
-    <t>Thiết kế các giao diện cho các vai trò của nhân viên</t>
-  </si>
-  <si>
     <t>Thiết kế giao diện cho các vai trò của Khách hàng</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>Lập trình thiết kế các giao diện cho các vai trò của Admin</t>
   </si>
   <si>
-    <t>Lập trình thiết kế các giao diện cho các vai trò của Nhân viên</t>
-  </si>
-  <si>
     <t>Lập trình thiết kế các giao diện cho các vai trò của Khách hàng</t>
   </si>
   <si>
@@ -152,9 +146,6 @@
     <t>Kiểm thử và sửa lại các giao diện cho các vai trò của Admin</t>
   </si>
   <si>
-    <t>Kiểm thử và sửa lại các giao diện cho các vai trò của Nhân viên</t>
-  </si>
-  <si>
     <t>Kiểm thử và sửa lại các giao diện cho các vai trò của Khách hàng</t>
   </si>
   <si>
@@ -179,9 +170,6 @@
     <t>Tạo các API cho các chức năng vai trò Admin</t>
   </si>
   <si>
-    <t>Tạo các API cho các chức năng vai trò Nhân viên</t>
-  </si>
-  <si>
     <t>Tạo các API cho các chức năng vai trò Khách hàng</t>
   </si>
   <si>
@@ -203,9 +191,6 @@
     <t>Kiểm thử các API cho các chức năng vai trò Admin trên Postman</t>
   </si>
   <si>
-    <t>Kiểm thử các API cho các chức năng vai trò Nhân viên trên Postman</t>
-  </si>
-  <si>
     <t>Kiểm thử các API cho các chức năng vai trò Khách hàng trên Postman</t>
   </si>
   <si>
@@ -281,9 +266,6 @@
     <t>Nguyễn Hải Nam</t>
   </si>
   <si>
-    <t>Xác định actor, usecase của vai trò quản lý</t>
-  </si>
-  <si>
     <t>3d</t>
   </si>
   <si>
@@ -306,6 +288,9 @@
   </si>
   <si>
     <t>20/4/2026</t>
+  </si>
+  <si>
+    <t>Xác định actor, usecase của vai trò khách hàng</t>
   </si>
 </sst>
 </file>
@@ -988,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC6D119-C27F-4AE4-B2F7-A5DC363917B5}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -1002,7 +987,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -1071,13 +1056,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>9</v>
@@ -1094,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>11</v>
@@ -1114,10 +1099,10 @@
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="8" t="s">
@@ -1135,10 +1120,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="8" t="s">
@@ -1153,13 +1138,13 @@
         <v>1.4</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="18" t="s">
@@ -1190,13 +1175,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>9</v>
@@ -1213,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>18</v>
@@ -1234,7 +1219,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>18</v>
@@ -1255,7 +1240,7 @@
         <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>18</v>
@@ -1269,74 +1254,74 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="9">
+      <c r="A16" s="14">
         <v>2.4</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="5"/>
+      <c r="F16" s="18" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="27">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="B17" s="5" t="s">
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>18</v>
-      </c>
+      <c r="B17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="19"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="6">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="11">
+        <v>46237</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G18" s="27">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6">
-        <v>3</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="11">
-        <v>46237</v>
-      </c>
+    <row r="19" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="1"/>
       <c r="F19" s="8" t="s">
         <v>9</v>
       </c>
@@ -1346,16 +1331,16 @@
     </row>
     <row r="20" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="8" t="s">
@@ -1367,16 +1352,16 @@
     </row>
     <row r="21" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="8" t="s">
@@ -1387,19 +1372,19 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="9">
-        <v>3.2</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="14">
+        <v>3.4</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="E22" s="22"/>
       <c r="F22" s="8" t="s">
         <v>9</v>
       </c>
@@ -1407,41 +1392,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="B23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="6">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="22"/>
       <c r="F24" s="8" t="s">
         <v>9</v>
       </c>
@@ -1449,33 +1426,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="4" t="s">
+    <row r="25" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6">
-        <v>4</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" t="s">
-        <v>86</v>
-      </c>
+      <c r="C26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="1"/>
       <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
@@ -1485,16 +1470,16 @@
     </row>
     <row r="27" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="9">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="8" t="s">
@@ -1505,19 +1490,19 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="9">
-        <v>4.2</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="E28" s="22"/>
       <c r="F28" s="8" t="s">
         <v>9</v>
       </c>
@@ -1525,687 +1510,586 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="6">
+        <v>5</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="C30" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6">
-        <v>5</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="E31" s="1"/>
+      <c r="F31" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="9">
+        <v>5.2</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" t="s">
-        <v>87</v>
-      </c>
+      <c r="C32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="9">
+        <v>5.3</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="1"/>
       <c r="F33" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33" s="21"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>43</v>
+    <row r="34" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="16">
+        <v>5.4</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="E34" s="22"/>
       <c r="F34" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="21"/>
-    </row>
-    <row r="35" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="9">
-        <v>5.2</v>
-      </c>
-      <c r="B35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="21"/>
-    </row>
-    <row r="36" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="9">
-        <v>5.3</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="1"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="6">
+        <v>6</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29">
+        <v>46207</v>
+      </c>
       <c r="F36" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G36" s="21"/>
     </row>
     <row r="37" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="9">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G37" s="21"/>
     </row>
     <row r="38" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="16">
-        <v>5.5</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>48</v>
+      <c r="A38" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="22"/>
+        <v>49</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="9">
+        <v>6.3</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="6">
-        <v>6</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="29">
-        <v>46207</v>
-      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40" s="21"/>
     </row>
     <row r="41" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="9">
-        <v>6.1</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>52</v>
+      <c r="A41" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="21"/>
-    </row>
-    <row r="42" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="9">
-        <v>6.2</v>
-      </c>
-      <c r="B42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="21"/>
-    </row>
-    <row r="43" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="9">
-        <v>6.3</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="B42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="21"/>
-    </row>
-    <row r="44" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="9">
-        <v>6.4</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6">
+        <v>5</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="A45" s="6">
+        <v>6</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="21"/>
-    </row>
-    <row r="46" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="14">
-        <v>6.6</v>
-      </c>
-      <c r="B46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="25">
+        <v>7</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="21"/>
+      <c r="F46" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="21"/>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="10">
+        <v>7.1</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="C47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="21"/>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E48" t="s">
-        <v>88</v>
-      </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="6">
-        <v>5</v>
-      </c>
-      <c r="B49" s="7" t="s">
+      <c r="A49" s="10">
+        <v>7.3</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="1"/>
+      <c r="E49" s="21"/>
       <c r="F49" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="6">
-        <v>6</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="A50" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="21"/>
       <c r="F50" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="25">
-        <v>7</v>
-      </c>
-      <c r="B51" s="7" t="s">
+      <c r="A51" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D51" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="21"/>
-      <c r="F51" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="21"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="2"/>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="21"/>
+      <c r="B52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="10">
-        <v>7.2</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="21"/>
+      <c r="A53" s="26">
+        <v>8</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21" t="s">
+        <v>83</v>
+      </c>
       <c r="F53" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G53" s="21"/>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="10">
-        <v>7.3</v>
+      <c r="A54" s="16">
+        <v>8.1</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E54" s="21"/>
       <c r="F54" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="10">
-        <v>7.4</v>
+      <c r="A55" s="16">
+        <v>8.1999999999999993</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="21"/>
     </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
-        <v>7.5</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>68</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="2"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" s="21"/>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="4" t="s">
+      <c r="A57" s="16">
+        <v>8.4</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="2"/>
+      <c r="C57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="21"/>
+      <c r="F57" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="21"/>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="26">
-        <v>8</v>
-      </c>
-      <c r="B58" s="7" t="s">
+      <c r="A58" s="16">
+        <v>8.5</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21" t="s">
-        <v>89</v>
-      </c>
+      <c r="C58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="21"/>
       <c r="F58" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G58" s="21"/>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G59" s="21"/>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="16">
-        <v>8.1999999999999993</v>
+      <c r="A60" s="10">
+        <v>8.6999999999999993</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G60" s="21"/>
-    </row>
-    <row r="61" spans="1:7" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="16">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="21"/>
-      <c r="F61" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="21"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="16">
-        <v>8.4</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="21"/>
-    </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="16">
-        <v>8.5</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="21"/>
-    </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="16">
-        <v>8.6</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="21"/>
-      <c r="F64" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="21"/>
-    </row>
-    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="10">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="21"/>
-      <c r="F65" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
